--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.350217468332669</v>
+        <v>1.519410338604059</v>
       </c>
       <c r="D2" t="n">
-        <v>9.667161600679089</v>
+        <v>1.570913760110352</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F2" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.14268954608401</v>
+        <v>2.623187051238652</v>
       </c>
       <c r="D3" t="n">
-        <v>16.91892431568863</v>
+        <v>2.749325201299403</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F3" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.52666118477116</v>
+        <v>5.285582442525315</v>
       </c>
       <c r="D4" t="n">
-        <v>31.47230081433445</v>
+        <v>5.114248882329349</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F4" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.22063439667686</v>
+        <v>2.473353089459989</v>
       </c>
       <c r="D5" t="n">
-        <v>14.05993230322203</v>
+        <v>2.284738999273579</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F5" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.73669006540468</v>
+        <v>2.882212135628261</v>
       </c>
       <c r="D6" t="n">
-        <v>17.05511757909237</v>
+        <v>2.77145660660251</v>
       </c>
       <c r="E6" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F6" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.72676445054619</v>
+        <v>4.505599223213756</v>
       </c>
       <c r="D7" t="n">
-        <v>18.53765454461071</v>
+        <v>3.01236886349924</v>
       </c>
       <c r="E7" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F7" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.09214536171049</v>
+        <v>3.427473621277954</v>
       </c>
       <c r="D8" t="n">
-        <v>22.40166761690421</v>
+        <v>3.640270987746935</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F8" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.14446357665089</v>
+        <v>7.33597533120577</v>
       </c>
       <c r="D9" t="n">
-        <v>33.09385713231439</v>
+        <v>5.377751784001089</v>
       </c>
       <c r="E9" t="n">
-        <v>10.7736163257119</v>
+        <v>1.750712652928183</v>
       </c>
       <c r="F9" t="n">
-        <v>7.664049659175626</v>
+        <v>1.245408069616039</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
